--- a/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R212-Equipement.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/CodeSystem-TRE-R212-Equipement.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="549">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250717120000</t>
+    <t>20250918120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-17T12:00:00+01:00</t>
+    <t>2025-09-18T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1279,10 +1279,16 @@
     <t>Polymorphisme mononucléotidique</t>
   </si>
   <si>
+    <t>Equipement qui permet d'identifier une différence génétique entre individus d’une même population qui se traduit par la variation d’une seule base (nucléotide) dans une séquence d’ADN, l’allèle minoritaire ayant une fréquence d’au moins 1 %. Ce type de variation, appelé aussi SNP (single nucleotide polymorphism), est très courant dans le génome humain et constitue une des principales sources de diversité individuelle. (Description scientifique de la nature et de la fréquence des SNP)</t>
+  </si>
+  <si>
     <t>174</t>
   </si>
   <si>
     <t>Hybridation génomique comparative (HGC)</t>
+  </si>
+  <si>
+    <t>Technique de cytogénétique moléculaire qui permet de repérer les variations du nombre de copies d’ADN (comme les duplications ou délétions) en comparant l’ADN d’un échantillon à un ADN de référence par marquage fluorescent. Cette méthode, utilisée en diagnostic notamment oncologique ou pour des anomalies constitutionnelles, offre une résolution plus fine qu’un caryotype classique.</t>
   </si>
   <si>
     <t>175</t>
@@ -4193,29 +4199,33 @@
       <c r="C174" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="D174" s="2"/>
+      <c r="D174" t="s" s="2">
+        <v>421</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
         <v>62</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="D175" s="2"/>
+        <v>423</v>
+      </c>
+      <c r="D175" t="s" s="2">
+        <v>424</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
         <v>62</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D176" s="2"/>
     </row>
@@ -4224,10 +4234,10 @@
         <v>62</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="D177" s="2"/>
     </row>
@@ -4236,10 +4246,10 @@
         <v>62</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="D178" s="2"/>
     </row>
@@ -4248,10 +4258,10 @@
         <v>62</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D179" s="2"/>
     </row>
@@ -4260,10 +4270,10 @@
         <v>62</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D180" s="2"/>
     </row>
@@ -4272,10 +4282,10 @@
         <v>62</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -4284,10 +4294,10 @@
         <v>62</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D182" s="2"/>
     </row>
@@ -4296,10 +4306,10 @@
         <v>62</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -4308,10 +4318,10 @@
         <v>62</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -4320,10 +4330,10 @@
         <v>62</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -4332,10 +4342,10 @@
         <v>62</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -4344,10 +4354,10 @@
         <v>62</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -4356,10 +4366,10 @@
         <v>62</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -4368,10 +4378,10 @@
         <v>62</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -4380,10 +4390,10 @@
         <v>62</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -4392,10 +4402,10 @@
         <v>62</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -4404,10 +4414,10 @@
         <v>62</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D192" s="2"/>
     </row>
@@ -4416,13 +4426,13 @@
         <v>62</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D193" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="194">
@@ -4430,10 +4440,10 @@
         <v>62</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D194" s="2"/>
     </row>
@@ -4442,10 +4452,10 @@
         <v>62</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -4454,10 +4464,10 @@
         <v>62</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D196" s="2"/>
     </row>
@@ -4466,10 +4476,10 @@
         <v>62</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D197" s="2"/>
     </row>
@@ -4478,10 +4488,10 @@
         <v>62</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -4490,10 +4500,10 @@
         <v>62</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -4502,13 +4512,13 @@
         <v>62</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D200" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="201">
@@ -4516,13 +4526,13 @@
         <v>62</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="D201" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="202">
@@ -4530,13 +4540,13 @@
         <v>62</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D202" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="203">
@@ -4544,13 +4554,13 @@
         <v>62</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="D203" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="204">
@@ -4558,13 +4568,13 @@
         <v>62</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D204" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="205">
@@ -4572,10 +4582,10 @@
         <v>62</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -4584,10 +4594,10 @@
         <v>62</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D206" s="2"/>
     </row>
@@ -4596,10 +4606,10 @@
         <v>62</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D207" s="2"/>
     </row>
@@ -4608,10 +4618,10 @@
         <v>62</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -4620,10 +4630,10 @@
         <v>62</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -4632,10 +4642,10 @@
         <v>62</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -4644,10 +4654,10 @@
         <v>62</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -4656,10 +4666,10 @@
         <v>62</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -4668,10 +4678,10 @@
         <v>62</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -4680,10 +4690,10 @@
         <v>62</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -4692,10 +4702,10 @@
         <v>62</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -4704,10 +4714,10 @@
         <v>62</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -4716,10 +4726,10 @@
         <v>62</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -4728,10 +4738,10 @@
         <v>62</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -4740,10 +4750,10 @@
         <v>62</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -4752,10 +4762,10 @@
         <v>62</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -4764,10 +4774,10 @@
         <v>62</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -4776,10 +4786,10 @@
         <v>62</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -4788,10 +4798,10 @@
         <v>62</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -4800,10 +4810,10 @@
         <v>62</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -4812,10 +4822,10 @@
         <v>62</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -4824,10 +4834,10 @@
         <v>62</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -4836,10 +4846,10 @@
         <v>62</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D227" s="2"/>
     </row>
@@ -4848,10 +4858,10 @@
         <v>62</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -4860,13 +4870,13 @@
         <v>62</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D229" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="230">
@@ -4874,10 +4884,10 @@
         <v>62</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -4886,10 +4896,10 @@
         <v>62</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D231" s="2"/>
     </row>
@@ -4898,10 +4908,10 @@
         <v>62</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D232" s="2"/>
     </row>
@@ -4910,10 +4920,10 @@
         <v>62</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D233" s="2"/>
     </row>
@@ -4925,7 +4935,7 @@
         <v>34</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D234" s="2"/>
     </row>
